--- a/inst/templates/mdJSONdictio_Dictionary_Template_v2.xlsx
+++ b/inst/templates/mdJSONdictio_Dictionary_Template_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/hannah_vincelette_fws_gov/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/hannah_vincelette_fws_gov/Documents/Documents/GitHub/mdJSONdictio/inst/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="52" documentId="11_365F113B0B881ECF37D0853E5545BA4ACE1F468E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A49469E-0F1D-4B80-B73C-7FB58FA28449}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="-3936" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -1959,21 +1959,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE904D578DFE6844BEAE84BDC2B4097E" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5270cfe5b55ea3ba0621c55bb260cb69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="847bd2b6-c417-48b3-84b7-e392c504f3bb" xmlns:ns4="f32a61f4-5698-46d5-9f56-343e6d7dc7d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f6d81c817a7b765436e9b6c5a88d8e2" ns3:_="" ns4:_="">
     <xsd:import namespace="847bd2b6-c417-48b3-84b7-e392c504f3bb"/>
@@ -2188,7 +2173,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CA5209D-AC5E-47D6-BDE1-DC1FA12E6F85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="847bd2b6-c417-48b3-84b7-e392c504f3bb"/>
+    <ds:schemaRef ds:uri="f32a61f4-5698-46d5-9f56-343e6d7dc7d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A7F80B6-A8F8-4FBE-8961-7EA21E322D52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -2205,29 +2224,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAD0FC99-4A9C-4418-97BD-C5AA74E03F40}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CA5209D-AC5E-47D6-BDE1-DC1FA12E6F85}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="847bd2b6-c417-48b3-84b7-e392c504f3bb"/>
-    <ds:schemaRef ds:uri="f32a61f4-5698-46d5-9f56-343e6d7dc7d7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/inst/templates/mdJSONdictio_Dictionary_Template_v2.xlsx
+++ b/inst/templates/mdJSONdictio_Dictionary_Template_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/hannah_vincelette_fws_gov/Documents/Documents/GitHub/mdJSONdictio/inst/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_365F113B0B881ECF37D0853E5545BA4ACE1F468E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A49469E-0F1D-4B80-B73C-7FB58FA28449}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_365F113B0B881ECF37D0853E5545BA4ACE1F468E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150E1770-8888-4E58-BD68-2B8884D7854B}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="-3936" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -414,11 +414,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,18 +705,18 @@
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1959,6 +1960,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE904D578DFE6844BEAE84BDC2B4097E" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5270cfe5b55ea3ba0621c55bb260cb69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="847bd2b6-c417-48b3-84b7-e392c504f3bb" xmlns:ns4="f32a61f4-5698-46d5-9f56-343e6d7dc7d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f6d81c817a7b765436e9b6c5a88d8e2" ns3:_="" ns4:_="">
     <xsd:import namespace="847bd2b6-c417-48b3-84b7-e392c504f3bb"/>
@@ -2173,36 +2189,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CA5209D-AC5E-47D6-BDE1-DC1FA12E6F85}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAD0FC99-4A9C-4418-97BD-C5AA74E03F40}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="847bd2b6-c417-48b3-84b7-e392c504f3bb"/>
-    <ds:schemaRef ds:uri="f32a61f4-5698-46d5-9f56-343e6d7dc7d7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2225,9 +2215,26 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAD0FC99-4A9C-4418-97BD-C5AA74E03F40}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CA5209D-AC5E-47D6-BDE1-DC1FA12E6F85}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="847bd2b6-c417-48b3-84b7-e392c504f3bb"/>
+    <ds:schemaRef ds:uri="f32a61f4-5698-46d5-9f56-343e6d7dc7d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>
+</clbl:labelList>
 </file>